--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8431-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8431-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0D2A53C-EDBB-4B93-B78A-E3935758EAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D5F03DE-5392-46A8-AB31-8B5CA360DBD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{44EF2515-A1D3-4CC9-8FBC-BD7A03C0CF67}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{C4B3E4D3-21F3-4DE1-8809-1A209D605D85}"/>
   </bookViews>
   <sheets>
     <sheet name="8431-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1529,30 +1529,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73561133-D48F-4970-BFCD-001FD3114052}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{244B49B5-69CD-4070-800A-8BFCF171E236}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="14" width="6.75" customWidth="1"/>
-    <col min="15" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="14" width="5.88671875" customWidth="1"/>
+    <col min="15" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1586,7 +1586,7 @@
       <c r="W1" s="32"/>
       <c r="X1" s="24"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1622,7 +1622,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="35"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="X3" s="38"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1742,7 +1742,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="39">
         <v>2025</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1962,7 +1962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="41">
         <v>2024</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="43"/>
       <c r="B9" s="44"/>
       <c r="C9" s="18" t="s">
@@ -2062,7 +2062,7 @@
       <c r="W9" s="50"/>
       <c r="X9" s="46"/>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
         <v>29</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="48"/>
       <c r="B11" s="48"/>
       <c r="C11" s="20" t="s">
@@ -2164,7 +2164,7 @@
       <c r="W11" s="50"/>
       <c r="X11" s="46"/>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2023</v>
       </c>
@@ -2384,7 +2384,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>29</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="53">
         <v>2022</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2021</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="53">
         <v>2020</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2019</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="53">
         <v>2018</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2017</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="53">
         <v>2016</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2015</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53">
         <v>2014</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>3.97</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2013</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="53">
         <v>2012</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2011</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="53">
         <v>2010</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39" t="s">
         <v>48</v>
       </c>
